--- a/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 24,61</t>
+          <t>-4,22; 24,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,36; -0,28</t>
+          <t>-25,79; -2,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 8,27</t>
+          <t>-24,7; 7,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 19,3</t>
+          <t>-18,7; 20,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 125,65</t>
+          <t>-13,03; 133,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,51; -0,3</t>
+          <t>-29,26; -2,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 11,34</t>
+          <t>-29,89; 10,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 61,82</t>
+          <t>-41,34; 64,35</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 4,23</t>
+          <t>-6,32; 4,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 4,35</t>
+          <t>-4,86; 4,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 7,08</t>
+          <t>-4,68; 6,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 1,37</t>
+          <t>-12,34; 1,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 16,54</t>
+          <t>-20,15; 16,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,32</t>
+          <t>-5,67; 5,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 11,05</t>
+          <t>-6,68; 10,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 4,02</t>
+          <t>-31,64; 3,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 11,67</t>
+          <t>-8,02; 11,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 10,76</t>
+          <t>-4,48; 9,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 1,86</t>
+          <t>-16,53; 0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 7,66</t>
+          <t>-8,97; 8,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 38,78</t>
+          <t>-19,76; 36,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 13,59</t>
+          <t>-5,19; 12,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 2,61</t>
+          <t>-20,99; 0,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 35,95</t>
+          <t>-30,16; 41,23</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,27</t>
+          <t>-3,61; 5,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,61</t>
+          <t>-4,95; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,75</t>
+          <t>-6,14; 2,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 1,56</t>
+          <t>-9,05; 1,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 18,98</t>
+          <t>-10,71; 21,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,13</t>
+          <t>-5,83; 3,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,09</t>
+          <t>-8,56; 4,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 4,85</t>
+          <t>-25,1; 4,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 24,65</t>
+          <t>-3,71; 24,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,79; -2,07</t>
+          <t>-26,19; 0,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 7,52</t>
+          <t>-22,32; 7,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 20,97</t>
+          <t>-19,47; 21,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 133,19</t>
+          <t>-11,71; 142,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,26; -2,78</t>
+          <t>-29,91; -0,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 10,86</t>
+          <t>-27,42; 11,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 64,35</t>
+          <t>-43,68; 64,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,5</t>
+          <t>-6,56; 4,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,17</t>
+          <t>-5,26; 4,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,87</t>
+          <t>-4,21; 7,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 1,08</t>
+          <t>-12,39; 1,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 16,64</t>
+          <t>-20,76; 16,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 5,06</t>
+          <t>-6,11; 5,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 10,76</t>
+          <t>-6,05; 11,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 3,2</t>
+          <t>-31,1; 3,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 11,13</t>
+          <t>-7,91; 11,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 9,98</t>
+          <t>-5,12; 10,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 0,46</t>
+          <t>-16,76; 1,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 8,21</t>
+          <t>-9,76; 7,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 36,77</t>
+          <t>-19,78; 37,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 12,68</t>
+          <t>-5,89; 13,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 0,64</t>
+          <t>-20,82; 1,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 41,23</t>
+          <t>-32,38; 39,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,98</t>
+          <t>-2,73; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,55</t>
+          <t>-4,89; 2,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 2,94</t>
+          <t>-6,41; 3,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 1,54</t>
+          <t>-8,75; 1,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 21,73</t>
+          <t>-8,18; 21,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,13</t>
+          <t>-5,7; 3,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 4,51</t>
+          <t>-9,01; 4,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 4,54</t>
+          <t>-23,89; 4,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,96%</t>
+          <t>-9,74%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 24,91</t>
+          <t>-3,08; 24,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 0,05</t>
+          <t>-26,36; -0,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 7,84</t>
+          <t>-22,37; 8,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 21,62</t>
+          <t>-19,77; 11,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 142,86</t>
+          <t>-10,68; 125,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -0,14</t>
+          <t>-29,51; -0,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 11,24</t>
+          <t>-27,67; 11,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 64,61</t>
+          <t>-41,93; 33,48</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,87</t>
+          <t>-3,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-13,18%</t>
+          <t>-9,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,32</t>
+          <t>-6,46; 4,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 4,61</t>
+          <t>-5,37; 4,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 7,38</t>
+          <t>-4,29; 7,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 1,32</t>
+          <t>-9,76; 2,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 16,13</t>
+          <t>-19,84; 16,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 5,63</t>
+          <t>-6,32; 5,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 11,47</t>
+          <t>-6,15; 11,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 3,74</t>
+          <t>-23,58; 6,43</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-2,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,26%</t>
+          <t>-8,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 11,21</t>
+          <t>-7,87; 11,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 10,4</t>
+          <t>-5,23; 10,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 1,18</t>
+          <t>-16,24; 1,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 7,91</t>
+          <t>-10,27; 5,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 37,56</t>
+          <t>-19,78; 38,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 13,12</t>
+          <t>-6,24; 13,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 1,67</t>
+          <t>-20,56; 2,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 39,46</t>
+          <t>-33,97; 27,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-3,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-10,11%</t>
+          <t>-9,04%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,0</t>
+          <t>-4,05; 5,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,97</t>
+          <t>-4,91; 2,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 3,07</t>
+          <t>-6,43; 2,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,4</t>
+          <t>-8,94; 1,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 21,65</t>
+          <t>-11,9; 18,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,7</t>
+          <t>-5,79; 3,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,61</t>
+          <t>-8,95; 4,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 4,48</t>
+          <t>-22,88; 5,24</t>
         </is>
       </c>
     </row>
